--- a/content/הקמה-moulded-pro-ii.xlsx
+++ b/content/הקמה-moulded-pro-ii.xlsx
@@ -257,10 +257,10 @@
         <v>15.08</v>
       </c>
       <c r="S2" s="0">
-        <v>49.9</v>
+        <v>69</v>
       </c>
       <c r="T2" s="0">
-        <v>24.95</v>
+        <v>34.5</v>
       </c>
       <c r="U2" s="0" t="inlineStr">
         <is>
@@ -353,10 +353,10 @@
         <v>15.08</v>
       </c>
       <c r="S3" s="0">
-        <v>49.9</v>
+        <v>69</v>
       </c>
       <c r="T3" s="0">
-        <v>24.95</v>
+        <v>34.5</v>
       </c>
       <c r="U3" s="0" t="inlineStr">
         <is>
@@ -449,10 +449,10 @@
         <v>15.08</v>
       </c>
       <c r="S4" s="0">
-        <v>49.9</v>
+        <v>69</v>
       </c>
       <c r="T4" s="0">
-        <v>24.95</v>
+        <v>34.5</v>
       </c>
       <c r="U4" s="0" t="inlineStr">
         <is>
